--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="161">
   <si>
     <t>Sezione</t>
   </si>
@@ -119,6 +119,12 @@
     <t>descrizioneMotivoRecupero</t>
   </si>
   <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
+  </si>
+  <si>
     <t>Data Matrimonio</t>
   </si>
   <si>
@@ -354,6 +360,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Generalità Sposa</t>
@@ -541,11 +553,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.0546875" customWidth="true" bestFit="true"/>
@@ -837,13 +849,13 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -857,16 +869,16 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -880,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -906,10 +918,10 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -932,7 +944,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -955,7 +967,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -978,7 +990,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -1001,7 +1013,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -1015,19 +1027,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -1038,16 +1050,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -1061,16 +1073,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -1084,16 +1096,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1107,7 +1119,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -1116,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1130,7 +1142,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -1139,7 +1151,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1153,7 +1165,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -1162,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1176,16 +1188,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1199,7 +1211,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1208,7 +1220,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1222,7 +1234,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1231,7 +1243,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1245,7 +1257,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1254,7 +1266,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1268,19 +1280,19 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1291,16 +1303,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1314,7 +1326,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1323,7 +1335,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1337,7 +1349,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>82</v>
@@ -1346,7 +1358,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>83</v>
@@ -1360,7 +1372,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
@@ -1369,7 +1381,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1383,7 +1395,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
@@ -1392,7 +1404,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1406,7 +1418,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
@@ -1415,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1429,7 +1441,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -1438,7 +1450,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1452,7 +1464,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
@@ -1461,7 +1473,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1475,7 +1487,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
@@ -1484,7 +1496,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1498,7 +1510,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
@@ -1507,7 +1519,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1521,7 +1533,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
@@ -1530,7 +1542,7 @@
         <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>99</v>
@@ -1544,16 +1556,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>101</v>
@@ -1567,7 +1579,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>102</v>
@@ -1576,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1590,16 +1602,16 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1613,7 +1625,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
@@ -1622,7 +1634,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1636,7 +1648,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
@@ -1645,7 +1657,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1659,7 +1671,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>110</v>
@@ -1668,7 +1680,7 @@
         <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>111</v>
@@ -1682,7 +1694,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>112</v>
@@ -1691,7 +1703,7 @@
         <v>25</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>113</v>
@@ -1705,19 +1717,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1728,19 +1740,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="E52" s="2" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1751,19 +1763,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1774,19 +1786,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1797,19 +1809,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1820,19 +1832,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1843,19 +1855,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1866,19 +1878,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1889,19 +1901,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1912,19 +1924,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1935,19 +1947,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -1958,19 +1970,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -1981,19 +1993,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2004,19 +2016,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2027,19 +2039,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2050,19 +2062,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2073,19 +2085,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2096,19 +2108,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2119,19 +2131,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2142,19 +2154,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2165,19 +2177,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2188,19 +2200,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2211,19 +2223,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2234,19 +2246,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2257,19 +2269,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2280,19 +2292,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2303,19 +2315,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2326,19 +2338,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2349,19 +2361,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2372,19 +2384,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2395,387 +2407,387 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="E96" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2786,19 +2798,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2809,19 +2821,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2832,19 +2844,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2855,19 +2867,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2878,19 +2890,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2901,7 +2913,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>135</v>
@@ -2910,10 +2922,10 @@
         <v>25</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2924,19 +2936,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -2947,19 +2959,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -2970,19 +2982,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -2993,19 +3005,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3016,19 +3028,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3039,19 +3051,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3062,19 +3074,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3085,19 +3097,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3108,19 +3120,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3131,19 +3143,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3154,19 +3166,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B114" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3177,19 +3189,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3200,7 +3212,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>135</v>
@@ -3209,10 +3221,10 @@
         <v>25</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3223,19 +3235,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3246,19 +3258,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3269,19 +3281,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3292,19 +3304,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3318,16 +3330,16 @@
         <v>149</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="E121" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3341,16 +3353,16 @@
         <v>149</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3361,19 +3373,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3384,24 +3396,93 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E124" s="2" t="s">
+      <c r="C127" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F124" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G124" s="2" t="s">
+      <c r="F127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="167">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -565,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
@@ -624,63 +630,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -689,90 +695,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -781,21 +787,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -804,21 +810,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -827,21 +833,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -850,21 +856,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -873,12 +879,12 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>37</v>
@@ -887,53 +893,53 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -942,21 +948,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -965,21 +971,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -988,21 +994,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -1011,21 +1017,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -1034,21 +1040,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -1057,44 +1063,44 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -1103,21 +1109,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1126,12 +1132,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -1140,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1149,21 +1155,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1172,21 +1178,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1195,12 +1201,12 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
@@ -1209,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1218,21 +1224,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1241,21 +1247,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1264,21 +1270,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1287,21 +1293,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1310,21 +1316,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1333,21 +1339,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1356,44 +1362,44 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1402,21 +1408,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1425,21 +1431,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1448,21 +1454,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1471,21 +1477,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1494,21 +1500,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1517,21 +1523,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1540,21 +1546,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>99</v>
@@ -1563,21 +1569,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>101</v>
@@ -1586,21 +1592,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1609,21 +1615,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1632,12 +1638,12 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
@@ -1646,7 +1652,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1655,21 +1661,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1678,21 +1684,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>111</v>
@@ -1701,21 +1707,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>113</v>
@@ -1724,21 +1730,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>115</v>
@@ -1747,21 +1753,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>117</v>
@@ -1770,21 +1776,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>119</v>
@@ -1793,21 +1799,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>121</v>
@@ -1816,44 +1822,44 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>60</v>
@@ -1862,21 +1868,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>62</v>
@@ -1885,12 +1891,12 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>63</v>
@@ -1899,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>64</v>
@@ -1908,21 +1914,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>66</v>
@@ -1931,21 +1937,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>68</v>
@@ -1954,12 +1960,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>69</v>
@@ -1968,7 +1974,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>70</v>
@@ -1977,21 +1983,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>72</v>
@@ -2000,21 +2006,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>74</v>
@@ -2023,21 +2029,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>76</v>
@@ -2046,21 +2052,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>78</v>
@@ -2069,21 +2075,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>80</v>
@@ -2092,21 +2098,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>82</v>
@@ -2115,44 +2121,44 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>85</v>
@@ -2161,21 +2167,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>87</v>
@@ -2184,21 +2190,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>89</v>
@@ -2207,21 +2213,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>91</v>
@@ -2230,21 +2236,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>93</v>
@@ -2253,21 +2259,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>95</v>
@@ -2276,21 +2282,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>97</v>
@@ -2299,21 +2305,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>99</v>
@@ -2322,21 +2328,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>101</v>
@@ -2345,21 +2351,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>103</v>
@@ -2368,21 +2374,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>105</v>
@@ -2391,12 +2397,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>106</v>
@@ -2405,7 +2411,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>107</v>
@@ -2414,21 +2420,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>109</v>
@@ -2437,21 +2443,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>111</v>
@@ -2460,21 +2466,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>113</v>
@@ -2483,21 +2489,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>115</v>
@@ -2506,21 +2512,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>117</v>
@@ -2529,21 +2535,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>119</v>
@@ -2552,21 +2558,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>121</v>
@@ -2575,7 +2581,7 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
@@ -2583,59 +2589,59 @@
         <v>124</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="E88" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>128</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="F89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>132</v>
@@ -2644,21 +2650,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>134</v>
@@ -2667,21 +2673,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>136</v>
@@ -2690,21 +2696,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>138</v>
@@ -2713,113 +2719,113 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>146</v>
@@ -2828,21 +2834,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>148</v>
@@ -2851,21 +2857,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>150</v>
@@ -2874,67 +2880,67 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="C101" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>132</v>
@@ -2943,21 +2949,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>134</v>
@@ -2966,21 +2972,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>136</v>
@@ -2989,21 +2995,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>138</v>
@@ -3012,113 +3018,113 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>146</v>
@@ -3127,21 +3133,21 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>148</v>
@@ -3150,21 +3156,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>150</v>
@@ -3173,7 +3179,7 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
@@ -3181,59 +3187,59 @@
         <v>153</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>154</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>132</v>
@@ -3242,21 +3248,21 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>134</v>
@@ -3265,21 +3271,21 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>136</v>
@@ -3288,21 +3294,21 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>138</v>
@@ -3311,113 +3317,113 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>146</v>
@@ -3426,21 +3432,21 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>148</v>
@@ -3449,21 +3455,21 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>150</v>
@@ -3472,7 +3478,7 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127">
@@ -3480,22 +3486,22 @@
         <v>155</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
@@ -3503,36 +3509,36 @@
         <v>157</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>162</v>
@@ -3541,21 +3547,21 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>164</v>
@@ -3564,30 +3570,53 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>16</v>
+      <c r="B132" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
